--- a/Config/Datas/wanted.xlsx
+++ b/Config/Datas/wanted.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17775" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="wanted_level_info" sheetId="3" r:id="rId1"/>
@@ -33,16 +33,16 @@
     <t>##var</t>
   </si>
   <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>need_val</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>need_val</t>
   </si>
   <si>
     <t>##group</t>
@@ -94,14 +94,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -557,148 +550,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1064,15 +1057,15 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -1172,7 +1165,6 @@
       <c r="B1" t="s">
         <v>9</v>
       </c>
-      <c r="C1"/>
       <c r="D1" t="s">
         <v>10</v>
       </c>
@@ -1182,14 +1174,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="C2"/>
       <c r="D2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -1202,7 +1193,6 @@
       <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3"/>
       <c r="D3" t="s">
         <v>6</v>
       </c>
@@ -1217,7 +1207,6 @@
       <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4"/>
       <c r="D4" t="s">
         <v>14</v>
       </c>

--- a/Config/Datas/wanted.xlsx
+++ b/Config/Datas/wanted.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,6 +574,11 @@
           <t>max_add_once</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>channel_cap</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -601,6 +606,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -628,6 +638,11 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -642,7 +657,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>每次基础增量(传入 AddWantedVal 的逻辑量，会再×1000)</t>
+          <t>每次基础增量(逻辑量，再×WantedValScale)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -652,7 +667,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>单次叠加封顶(逻辑量，0=不限制)与 add_wanted 取较小</t>
+          <t>单次事件封顶(逻辑量，0=不限制)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>该罪类通道累计上限(逻辑量，0=不限制)；全局通缉=各通道max</t>
         </is>
       </c>
     </row>
@@ -671,6 +691,9 @@
       <c r="E5" t="n">
         <v>8</v>
       </c>
+      <c r="F5" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -687,6 +710,9 @@
       <c r="E6" t="n">
         <v>15</v>
       </c>
+      <c r="F6" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -702,6 +728,28 @@
       </c>
       <c r="E7" t="n">
         <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ForceExtractAssault</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F8" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/wanted.xlsx
+++ b/Config/Datas/wanted.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="wanted_level_info" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,31 +11,368 @@
     <sheet name="wanted_guard_spawn" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="21">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -44,15 +380,305 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -405,7 +1031,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -416,7 +1041,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -546,7 +1171,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -763,8 +1388,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -807,6 +1432,21 @@
           <t>cull_distance</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>min_alert_tier</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>pressure_behavior</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>patrol_pick_n</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -849,6 +1489,21 @@
           <t>float</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -891,6 +1546,21 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -931,6 +1601,21 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>超出距离销毁</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>区域警戒档位下限，满足则本行可按警戒参与选用；999 表示仅靠通缉星</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>压力行为枚举占位，对应动态守卫 AI/移动策略</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>巡逻路网抽样数，&lt;=0 用控制器默认 3</t>
         </is>
       </c>
     </row>
@@ -958,6 +1643,15 @@
       <c r="H5" t="n">
         <v>40</v>
       </c>
+      <c r="I5" t="n">
+        <v>999</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -983,6 +1677,15 @@
       <c r="H6" t="n">
         <v>36</v>
       </c>
+      <c r="I6" t="n">
+        <v>999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -1008,6 +1711,15 @@
       <c r="H7" t="n">
         <v>34</v>
       </c>
+      <c r="I7" t="n">
+        <v>999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -1033,6 +1745,15 @@
       <c r="H8" t="n">
         <v>32</v>
       </c>
+      <c r="I8" t="n">
+        <v>999</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -1057,6 +1778,15 @@
       </c>
       <c r="H9" t="n">
         <v>30</v>
+      </c>
+      <c r="I9" t="n">
+        <v>999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
